--- a/workpaper_templates/WP08_Going_Concern_Assessment.xlsx
+++ b/workpaper_templates/WP08_Going_Concern_Assessment.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +59,17 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +202,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -196,13 +221,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -667,15 +709,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Concern? (Y/N)</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
@@ -687,15 +733,18 @@
           <t>Net current assets / (liabilities)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="11">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -703,15 +752,18 @@
           <t>Net assets / (liabilities)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="11">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -719,15 +771,18 @@
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="11">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -735,15 +790,18 @@
           <t>Revenue trend</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -751,15 +809,18 @@
           <t>Interest coverage ratio</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="11">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -767,15 +828,18 @@
           <t>Debt / equity ratio</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
+      <c r="B11" s="10" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="11">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1">
       <c r="A12" s="5" t="n"/>
@@ -830,15 +894,15 @@
           <t>Key customer / supplier dependency</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="B15" s="12" t="inlineStr"/>
+      <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -846,15 +910,15 @@
           <t>Loss of key personnel</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -862,15 +926,15 @@
           <t>Legal proceedings</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr"/>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="B17" s="12" t="inlineStr"/>
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -878,15 +942,15 @@
           <t>Regulatory compliance</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr"/>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="B18" s="12" t="inlineStr"/>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -894,15 +958,15 @@
           <t>Access to finance</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr"/>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
+      <c r="B19" s="12" t="inlineStr"/>
+      <c r="C19" s="12" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
     </row>
     <row r="20" ht="6" customHeight="1">
       <c r="A20" s="5" t="n"/>
@@ -952,64 +1016,64 @@
       <c r="J22" s="8" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr"/>
-      <c r="C23" s="9" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="A24" s="12" t="inlineStr"/>
+      <c r="B24" s="12" t="inlineStr"/>
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="12" t="inlineStr"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="9" t="inlineStr"/>
-      <c r="C26" s="9" t="inlineStr"/>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
+      <c r="A26" s="12" t="inlineStr"/>
+      <c r="B26" s="12" t="inlineStr"/>
+      <c r="C26" s="12" t="inlineStr"/>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="9" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr"/>
-      <c r="C27" s="9" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
+      <c r="A27" s="12" t="inlineStr"/>
+      <c r="B27" s="12" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
     </row>
     <row r="28" ht="6" customHeight="1">
       <c r="A28" s="5" t="n"/>
@@ -1059,28 +1123,28 @@
       <c r="J30" s="8" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
+      <c r="A31" s="12" t="inlineStr"/>
+      <c r="B31" s="12" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
+      <c r="A32" s="12" t="inlineStr"/>
+      <c r="B32" s="12" t="inlineStr"/>
+      <c r="C32" s="12" t="inlineStr"/>
+      <c r="D32" s="12" t="inlineStr"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
     </row>
     <row r="33" ht="6" customHeight="1">
       <c r="A33" s="5" t="n"/>
@@ -1102,52 +1166,52 @@
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="11" t="n"/>
+      <c r="A35" s="13" t="inlineStr"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="9" t="inlineStr"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="11" t="n"/>
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="9" t="inlineStr"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="11" t="n"/>
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="11" t="n"/>
+      <c r="A38" s="13" t="inlineStr"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39" ht="6" customHeight="1">
       <c r="A39" s="5" t="n"/>
@@ -1169,84 +1233,84 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>{{preparer}}</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>{{date_prepared}}</t>
         </is>
       </c>
-      <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
+      <c r="H41" s="19" t="n"/>
+      <c r="I41" s="19" t="n"/>
+      <c r="J41" s="19" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>{{reviewer}}</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>{{date_reviewed}}</t>
         </is>
       </c>
-      <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
+      <c r="J42" s="19" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr"/>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
-      <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
+      <c r="B43" s="19" t="inlineStr"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19" t="n"/>
+      <c r="J43" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1269,6 +1333,14 @@
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="G42:J42"/>
   </mergeCells>
+  <conditionalFormatting sqref="D6:D11">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>